--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590766</v>
+        <v>121590637</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732714</v>
+        <v>733345</v>
       </c>
       <c r="R2" t="n">
-        <v>7358659</v>
+        <v>7358499</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590744</v>
+        <v>121590761</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>92012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733121</v>
+        <v>732713</v>
       </c>
       <c r="R4" t="n">
-        <v>7358408</v>
+        <v>7358624</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +980,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590746</v>
+        <v>121590733</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1036,16 +1044,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>732917</v>
+        <v>733285</v>
       </c>
       <c r="R5" t="n">
-        <v>7358580</v>
+        <v>7358339</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal kolad tallstubbe</t>
+          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590751</v>
+        <v>121590759</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>90967</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1137,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>732715</v>
+        <v>732625</v>
       </c>
       <c r="R6" t="n">
-        <v>7358583</v>
+        <v>7358605</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,6 +1205,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590756</v>
+        <v>121590760</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,26 +1252,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>732650</v>
+        <v>732679</v>
       </c>
       <c r="R7" t="n">
-        <v>7358579</v>
+        <v>7358623</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590767</v>
+        <v>121590749</v>
       </c>
       <c r="B8" t="n">
-        <v>79718</v>
+        <v>91990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,30 +1354,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1365,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>732723</v>
+        <v>732814</v>
       </c>
       <c r="R8" t="n">
-        <v>7358678</v>
+        <v>7358528</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590764</v>
+        <v>121590748</v>
       </c>
       <c r="B9" t="n">
-        <v>91990</v>
+        <v>91988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,26 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1471,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>732711</v>
+        <v>732822</v>
       </c>
       <c r="R9" t="n">
-        <v>7358653</v>
+        <v>7358527</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590727</v>
+        <v>121590764</v>
       </c>
       <c r="B10" t="n">
-        <v>82393</v>
+        <v>91990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,26 +1570,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1577,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733444</v>
+        <v>732711</v>
       </c>
       <c r="R10" t="n">
-        <v>7358349</v>
+        <v>7358653</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,11 +1634,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590749</v>
+        <v>121590747</v>
       </c>
       <c r="B11" t="n">
-        <v>91990</v>
+        <v>77541</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,26 +1676,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>732814</v>
+        <v>732908</v>
       </c>
       <c r="R11" t="n">
-        <v>7358528</v>
+        <v>7358595</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,6 +1740,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590735</v>
+        <v>121590752</v>
       </c>
       <c r="B12" t="n">
-        <v>92024</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,38 +1787,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733263</v>
+        <v>732711</v>
       </c>
       <c r="R12" t="n">
-        <v>7358369</v>
+        <v>7358587</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,6 +1859,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590743</v>
+        <v>121590746</v>
       </c>
       <c r="B13" t="n">
-        <v>77541</v>
+        <v>79227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1906,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1900,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733124</v>
+        <v>732917</v>
       </c>
       <c r="R13" t="n">
-        <v>7358421</v>
+        <v>7358580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1940,7 +1974,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590729</v>
+        <v>121590767</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>79718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +2017,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733332</v>
+        <v>732723</v>
       </c>
       <c r="R14" t="n">
-        <v>7358386</v>
+        <v>7358678</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590761</v>
+        <v>121590636</v>
       </c>
       <c r="B15" t="n">
-        <v>92012</v>
+        <v>97065</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2119,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2117,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>732713</v>
+        <v>733108</v>
       </c>
       <c r="R15" t="n">
-        <v>7358624</v>
+        <v>7358536</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2147,12 +2181,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590733</v>
+        <v>121590765</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,50 +2225,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733285</v>
+        <v>732711</v>
       </c>
       <c r="R16" t="n">
-        <v>7358339</v>
+        <v>7358653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2267,11 +2293,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590752</v>
+        <v>121590756</v>
       </c>
       <c r="B17" t="n">
-        <v>57509</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,25 +2331,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2336,24 +2357,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>732711</v>
+        <v>732650</v>
       </c>
       <c r="R17" t="n">
-        <v>7358587</v>
+        <v>7358579</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,11 +2399,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590757</v>
+        <v>121590742</v>
       </c>
       <c r="B18" t="n">
-        <v>78691</v>
+        <v>77993</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,21 +2441,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2461,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>732625</v>
+        <v>733122</v>
       </c>
       <c r="R18" t="n">
-        <v>7358580</v>
+        <v>7358420</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2501,7 +2509,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,10 +2536,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590758</v>
+        <v>121590766</v>
       </c>
       <c r="B19" t="n">
-        <v>82393</v>
+        <v>91996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,30 +2548,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2572,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>732625</v>
+        <v>732714</v>
       </c>
       <c r="R19" t="n">
-        <v>7358560</v>
+        <v>7358659</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,11 +2616,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590765</v>
+        <v>121590745</v>
       </c>
       <c r="B20" t="n">
-        <v>91996</v>
+        <v>89769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,30 +2654,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2683,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>732711</v>
+        <v>732960</v>
       </c>
       <c r="R20" t="n">
-        <v>7358653</v>
+        <v>7358509</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2745,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590763</v>
+        <v>121590730</v>
       </c>
       <c r="B21" t="n">
-        <v>92012</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,25 +2760,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2789,10 +2792,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>732706</v>
+        <v>733305</v>
       </c>
       <c r="R21" t="n">
-        <v>7358642</v>
+        <v>7358389</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2825,6 +2828,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590736</v>
+        <v>121590727</v>
       </c>
       <c r="B22" t="n">
-        <v>91996</v>
+        <v>82393</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2863,30 +2871,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2895,10 +2903,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733159</v>
+        <v>733444</v>
       </c>
       <c r="R22" t="n">
-        <v>7358335</v>
+        <v>7358349</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2931,6 +2939,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590742</v>
+        <v>121590728</v>
       </c>
       <c r="B23" t="n">
-        <v>77993</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,21 +2986,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3001,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733122</v>
+        <v>733332</v>
       </c>
       <c r="R23" t="n">
-        <v>7358420</v>
+        <v>7358429</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3041,7 +3054,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,10 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590632</v>
+        <v>121590735</v>
       </c>
       <c r="B24" t="n">
-        <v>82393</v>
+        <v>92024</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,26 +3097,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3112,10 +3125,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>732883</v>
+        <v>733263</v>
       </c>
       <c r="R24" t="n">
-        <v>7358415</v>
+        <v>7358369</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3142,12 +3155,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,10 +3187,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590728</v>
+        <v>121590631</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>97065</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,25 +3199,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3218,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733332</v>
+        <v>733042</v>
       </c>
       <c r="R25" t="n">
-        <v>7358429</v>
+        <v>7358712</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3248,17 +3261,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tallöverståndare</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590731</v>
+        <v>121590744</v>
       </c>
       <c r="B26" t="n">
-        <v>82393</v>
+        <v>79198</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3301,21 +3309,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3329,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733309</v>
+        <v>733121</v>
       </c>
       <c r="R26" t="n">
-        <v>7358348</v>
+        <v>7358408</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3369,7 +3377,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3396,10 +3404,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590631</v>
+        <v>121590763</v>
       </c>
       <c r="B27" t="n">
-        <v>97065</v>
+        <v>92012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,25 +3416,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3440,10 +3448,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733042</v>
+        <v>732706</v>
       </c>
       <c r="R27" t="n">
-        <v>7358712</v>
+        <v>7358642</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3470,12 +3478,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590762</v>
+        <v>121590750</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>91990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3514,30 +3522,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3546,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>732698</v>
+        <v>732744</v>
       </c>
       <c r="R28" t="n">
-        <v>7358638</v>
+        <v>7358602</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3608,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590759</v>
+        <v>121590632</v>
       </c>
       <c r="B29" t="n">
-        <v>90967</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3652,10 +3660,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>732625</v>
+        <v>732883</v>
       </c>
       <c r="R29" t="n">
-        <v>7358605</v>
+        <v>7358415</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3682,17 +3690,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3719,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590745</v>
+        <v>121590731</v>
       </c>
       <c r="B30" t="n">
-        <v>89769</v>
+        <v>82393</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,21 +3738,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3763,10 +3766,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>732960</v>
+        <v>733309</v>
       </c>
       <c r="R30" t="n">
-        <v>7358509</v>
+        <v>7358348</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,6 +3802,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3833,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590636</v>
+        <v>121590736</v>
       </c>
       <c r="B31" t="n">
-        <v>97065</v>
+        <v>91996</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,26 +3849,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3869,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733108</v>
+        <v>733159</v>
       </c>
       <c r="R31" t="n">
-        <v>7358536</v>
+        <v>7358335</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3899,12 +3907,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3931,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590730</v>
+        <v>121590758</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>82393</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,25 +3951,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3975,10 +3983,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733305</v>
+        <v>732625</v>
       </c>
       <c r="R32" t="n">
-        <v>7358389</v>
+        <v>7358560</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4015,7 +4023,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På grov gammal sälg</t>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590750</v>
+        <v>121590762</v>
       </c>
       <c r="B33" t="n">
-        <v>91990</v>
+        <v>91996</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4054,30 +4062,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4086,10 +4094,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>732744</v>
+        <v>732698</v>
       </c>
       <c r="R33" t="n">
-        <v>7358602</v>
+        <v>7358638</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4148,10 +4156,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590760</v>
+        <v>121590757</v>
       </c>
       <c r="B34" t="n">
-        <v>91996</v>
+        <v>78691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,30 +4168,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4192,10 +4200,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732679</v>
+        <v>732625</v>
       </c>
       <c r="R34" t="n">
-        <v>7358623</v>
+        <v>7358580</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4228,6 +4236,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,10 +4267,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590748</v>
+        <v>121590729</v>
       </c>
       <c r="B35" t="n">
-        <v>91988</v>
+        <v>97059</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4266,30 +4279,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4298,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732822</v>
+        <v>733332</v>
       </c>
       <c r="R35" t="n">
-        <v>7358527</v>
+        <v>7358386</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4360,10 +4373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590637</v>
+        <v>121590751</v>
       </c>
       <c r="B36" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4372,50 +4385,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>733345</v>
+        <v>732715</v>
       </c>
       <c r="R36" t="n">
-        <v>7358499</v>
+        <v>7358583</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4442,17 +4447,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,7 +4479,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590747</v>
+        <v>121590743</v>
       </c>
       <c r="B37" t="n">
         <v>77541</v>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732908</v>
+        <v>733124</v>
       </c>
       <c r="R37" t="n">
-        <v>7358595</v>
+        <v>7358421</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammalt talltorrträd</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590637</v>
+        <v>121590766</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733345</v>
+        <v>732714</v>
       </c>
       <c r="R2" t="n">
-        <v>7358499</v>
+        <v>7358659</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590726</v>
+        <v>121590736</v>
       </c>
       <c r="B3" t="n">
         <v>91996</v>
@@ -829,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733444</v>
+        <v>733159</v>
       </c>
       <c r="R3" t="n">
-        <v>7358349</v>
+        <v>7358335</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590761</v>
+        <v>121590742</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>77993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>732713</v>
+        <v>733122</v>
       </c>
       <c r="R4" t="n">
-        <v>7358624</v>
+        <v>7358420</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590733</v>
+        <v>121590746</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>79227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1044,24 +1036,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733285</v>
+        <v>732917</v>
       </c>
       <c r="R5" t="n">
-        <v>7358339</v>
+        <v>7358580</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flygande, läte</t>
+          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590759</v>
+        <v>121590763</v>
       </c>
       <c r="B6" t="n">
-        <v>90967</v>
+        <v>92012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>732625</v>
+        <v>732706</v>
       </c>
       <c r="R6" t="n">
-        <v>7358605</v>
+        <v>7358642</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590760</v>
+        <v>121590632</v>
       </c>
       <c r="B7" t="n">
-        <v>91996</v>
+        <v>82393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,30 +1227,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>732679</v>
+        <v>732883</v>
       </c>
       <c r="R7" t="n">
-        <v>7358623</v>
+        <v>7358415</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590749</v>
+        <v>121590758</v>
       </c>
       <c r="B8" t="n">
-        <v>91990</v>
+        <v>82393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,26 +1337,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1386,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>732814</v>
+        <v>732625</v>
       </c>
       <c r="R8" t="n">
-        <v>7358528</v>
+        <v>7358560</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,6 +1401,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590748</v>
+        <v>121590727</v>
       </c>
       <c r="B9" t="n">
-        <v>91988</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,26 +1448,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1492,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>732822</v>
+        <v>733444</v>
       </c>
       <c r="R9" t="n">
-        <v>7358527</v>
+        <v>7358349</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,6 +1512,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590764</v>
+        <v>121590751</v>
       </c>
       <c r="B10" t="n">
-        <v>91990</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,30 +1555,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1598,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>732711</v>
+        <v>732715</v>
       </c>
       <c r="R10" t="n">
-        <v>7358653</v>
+        <v>7358583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1771,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590752</v>
+        <v>121590744</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>79198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1809,24 +1798,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>732711</v>
+        <v>733121</v>
       </c>
       <c r="R12" t="n">
-        <v>7358587</v>
+        <v>7358408</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,7 +1844,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590746</v>
+        <v>121590735</v>
       </c>
       <c r="B13" t="n">
-        <v>79227</v>
+        <v>92024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,26 +1887,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1934,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>732917</v>
+        <v>733263</v>
       </c>
       <c r="R13" t="n">
-        <v>7358580</v>
+        <v>7358369</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,11 +1951,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590767</v>
+        <v>121590733</v>
       </c>
       <c r="B14" t="n">
-        <v>79718</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,25 +1989,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2039,16 +2015,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>732723</v>
+        <v>733285</v>
       </c>
       <c r="R14" t="n">
-        <v>7358678</v>
+        <v>7358339</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,6 +2065,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590765</v>
+        <v>121590757</v>
       </c>
       <c r="B16" t="n">
-        <v>91996</v>
+        <v>78691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2225,30 +2214,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2257,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>732711</v>
+        <v>732625</v>
       </c>
       <c r="R16" t="n">
-        <v>7358653</v>
+        <v>7358580</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2293,6 +2282,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590756</v>
+        <v>121590748</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>91988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2331,30 +2325,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2363,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>732650</v>
+        <v>732822</v>
       </c>
       <c r="R17" t="n">
-        <v>7358579</v>
+        <v>7358527</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2425,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590742</v>
+        <v>121590764</v>
       </c>
       <c r="B18" t="n">
-        <v>77993</v>
+        <v>91990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,26 +2435,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2469,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733122</v>
+        <v>732711</v>
       </c>
       <c r="R18" t="n">
-        <v>7358420</v>
+        <v>7358653</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2505,11 +2499,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590766</v>
+        <v>121590767</v>
       </c>
       <c r="B19" t="n">
-        <v>91996</v>
+        <v>79718</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,26 +2541,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2580,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>732714</v>
+        <v>732723</v>
       </c>
       <c r="R19" t="n">
-        <v>7358659</v>
+        <v>7358678</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2642,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590745</v>
+        <v>121590728</v>
       </c>
       <c r="B20" t="n">
-        <v>89769</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2686,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>732960</v>
+        <v>733332</v>
       </c>
       <c r="R20" t="n">
-        <v>7358509</v>
+        <v>7358429</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2722,6 +2711,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590730</v>
+        <v>121590745</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>89769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,25 +2754,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2792,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733305</v>
+        <v>732960</v>
       </c>
       <c r="R21" t="n">
-        <v>7358389</v>
+        <v>7358509</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2828,11 +2822,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,10 +2848,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590727</v>
+        <v>121590743</v>
       </c>
       <c r="B22" t="n">
-        <v>82393</v>
+        <v>77541</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,21 +2864,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2903,10 +2892,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733444</v>
+        <v>733124</v>
       </c>
       <c r="R22" t="n">
-        <v>7358349</v>
+        <v>7358421</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2943,7 +2932,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,10 +2959,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590728</v>
+        <v>121590761</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>92012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2986,21 +2975,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3014,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733332</v>
+        <v>732713</v>
       </c>
       <c r="R23" t="n">
-        <v>7358429</v>
+        <v>7358624</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3050,11 +3039,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590735</v>
+        <v>121590726</v>
       </c>
       <c r="B24" t="n">
-        <v>92024</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,30 +3077,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3125,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733263</v>
+        <v>733444</v>
       </c>
       <c r="R24" t="n">
-        <v>7358369</v>
+        <v>7358349</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3187,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590631</v>
+        <v>121590730</v>
       </c>
       <c r="B25" t="n">
-        <v>97065</v>
+        <v>79726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3203,21 +3187,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3231,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733042</v>
+        <v>733305</v>
       </c>
       <c r="R25" t="n">
-        <v>7358712</v>
+        <v>7358389</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3261,12 +3245,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590744</v>
+        <v>121590631</v>
       </c>
       <c r="B26" t="n">
-        <v>79198</v>
+        <v>97065</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3305,25 +3294,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3337,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733121</v>
+        <v>733042</v>
       </c>
       <c r="R26" t="n">
-        <v>7358408</v>
+        <v>7358712</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3367,17 +3356,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590763</v>
+        <v>121590750</v>
       </c>
       <c r="B27" t="n">
-        <v>92012</v>
+        <v>91990</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,26 +3404,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3448,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>732706</v>
+        <v>732744</v>
       </c>
       <c r="R27" t="n">
-        <v>7358642</v>
+        <v>7358602</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3510,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590750</v>
+        <v>121590749</v>
       </c>
       <c r="B28" t="n">
         <v>91990</v>
@@ -3554,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>732744</v>
+        <v>732814</v>
       </c>
       <c r="R28" t="n">
-        <v>7358602</v>
+        <v>7358528</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3616,10 +3600,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590632</v>
+        <v>121590729</v>
       </c>
       <c r="B29" t="n">
-        <v>82393</v>
+        <v>97059</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,25 +3612,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3660,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>732883</v>
+        <v>733332</v>
       </c>
       <c r="R29" t="n">
-        <v>7358415</v>
+        <v>7358386</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3690,12 +3674,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,10 +3706,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590731</v>
+        <v>121590756</v>
       </c>
       <c r="B30" t="n">
-        <v>82393</v>
+        <v>97059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3734,25 +3718,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3766,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733309</v>
+        <v>732650</v>
       </c>
       <c r="R30" t="n">
-        <v>7358348</v>
+        <v>7358579</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3802,11 +3786,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3833,7 +3812,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590736</v>
+        <v>121590760</v>
       </c>
       <c r="B31" t="n">
         <v>91996</v>
@@ -3868,7 +3847,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3877,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733159</v>
+        <v>732679</v>
       </c>
       <c r="R31" t="n">
-        <v>7358335</v>
+        <v>7358623</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3939,10 +3918,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590758</v>
+        <v>121590637</v>
       </c>
       <c r="B32" t="n">
-        <v>82393</v>
+        <v>57509</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3955,21 +3934,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3977,16 +3956,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>732625</v>
+        <v>733345</v>
       </c>
       <c r="R32" t="n">
-        <v>7358560</v>
+        <v>7358499</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4013,17 +4000,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,10 +4037,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590762</v>
+        <v>121590731</v>
       </c>
       <c r="B33" t="n">
-        <v>91996</v>
+        <v>82393</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,30 +4049,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4094,10 +4081,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>732698</v>
+        <v>733309</v>
       </c>
       <c r="R33" t="n">
-        <v>7358638</v>
+        <v>7358348</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4130,6 +4117,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4156,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590757</v>
+        <v>121590752</v>
       </c>
       <c r="B34" t="n">
-        <v>78691</v>
+        <v>57509</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4172,21 +4164,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4194,16 +4186,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732625</v>
+        <v>732711</v>
       </c>
       <c r="R34" t="n">
-        <v>7358580</v>
+        <v>7358587</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4267,10 +4267,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590729</v>
+        <v>121590759</v>
       </c>
       <c r="B35" t="n">
-        <v>97059</v>
+        <v>90967</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,25 +4279,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>65</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733332</v>
+        <v>732625</v>
       </c>
       <c r="R35" t="n">
-        <v>7358386</v>
+        <v>7358605</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4347,6 +4347,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4373,7 +4378,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590751</v>
+        <v>121590765</v>
       </c>
       <c r="B36" t="n">
         <v>91996</v>
@@ -4408,7 +4413,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732715</v>
+        <v>732711</v>
       </c>
       <c r="R36" t="n">
-        <v>7358583</v>
+        <v>7358653</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4479,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590743</v>
+        <v>121590762</v>
       </c>
       <c r="B37" t="n">
-        <v>77541</v>
+        <v>91996</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,30 +4496,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733124</v>
+        <v>732698</v>
       </c>
       <c r="R37" t="n">
-        <v>7358421</v>
+        <v>7358638</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4559,11 +4564,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590636</v>
+        <v>121590757</v>
       </c>
       <c r="B15" t="n">
-        <v>97065</v>
+        <v>78691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,25 +2108,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733108</v>
+        <v>732625</v>
       </c>
       <c r="R15" t="n">
-        <v>7358536</v>
+        <v>7358580</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,12 +2170,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590757</v>
+        <v>121590748</v>
       </c>
       <c r="B16" t="n">
-        <v>78691</v>
+        <v>91988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,26 +2223,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2246,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>732625</v>
+        <v>732822</v>
       </c>
       <c r="R16" t="n">
-        <v>7358580</v>
+        <v>7358527</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2282,11 +2287,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590748</v>
+        <v>121590636</v>
       </c>
       <c r="B17" t="n">
-        <v>91988</v>
+        <v>97065</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,30 +2325,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>732822</v>
+        <v>733108</v>
       </c>
       <c r="R17" t="n">
-        <v>7358527</v>
+        <v>7358536</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590752</v>
+        <v>121590759</v>
       </c>
       <c r="B34" t="n">
-        <v>57509</v>
+        <v>90967</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4186,24 +4186,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732711</v>
+        <v>732625</v>
       </c>
       <c r="R34" t="n">
-        <v>7358587</v>
+        <v>7358605</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4240,7 +4232,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4267,10 +4259,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590759</v>
+        <v>121590765</v>
       </c>
       <c r="B35" t="n">
-        <v>90967</v>
+        <v>91996</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,30 +4271,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4311,10 +4303,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732625</v>
+        <v>732711</v>
       </c>
       <c r="R35" t="n">
-        <v>7358605</v>
+        <v>7358653</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4347,11 +4339,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,7 +4365,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590765</v>
+        <v>121590762</v>
       </c>
       <c r="B36" t="n">
         <v>91996</v>
@@ -4413,7 +4400,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4422,10 +4409,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732711</v>
+        <v>732698</v>
       </c>
       <c r="R36" t="n">
-        <v>7358653</v>
+        <v>7358638</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4484,10 +4471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590762</v>
+        <v>121590752</v>
       </c>
       <c r="B37" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4496,42 +4483,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732698</v>
+        <v>732711</v>
       </c>
       <c r="R37" t="n">
-        <v>7358638</v>
+        <v>7358587</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4564,6 +4559,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590759</v>
+        <v>121590752</v>
       </c>
       <c r="B34" t="n">
-        <v>90967</v>
+        <v>57509</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4186,16 +4186,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732625</v>
+        <v>732711</v>
       </c>
       <c r="R34" t="n">
-        <v>7358605</v>
+        <v>7358587</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4232,7 +4240,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal halvt nedbruten barrved</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,10 +4267,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590765</v>
+        <v>121590759</v>
       </c>
       <c r="B35" t="n">
-        <v>91996</v>
+        <v>90967</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4271,30 +4279,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4303,10 +4311,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732711</v>
+        <v>732625</v>
       </c>
       <c r="R35" t="n">
-        <v>7358653</v>
+        <v>7358605</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4339,6 +4347,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,7 +4378,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590762</v>
+        <v>121590765</v>
       </c>
       <c r="B36" t="n">
         <v>91996</v>
@@ -4400,7 +4413,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4409,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732698</v>
+        <v>732711</v>
       </c>
       <c r="R36" t="n">
-        <v>7358638</v>
+        <v>7358653</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4471,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590752</v>
+        <v>121590762</v>
       </c>
       <c r="B37" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4483,50 +4496,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732711</v>
+        <v>732698</v>
       </c>
       <c r="R37" t="n">
-        <v>7358587</v>
+        <v>7358638</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4559,11 +4564,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590766</v>
+        <v>121590757</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>78698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732714</v>
+        <v>732625</v>
       </c>
       <c r="R2" t="n">
-        <v>7358659</v>
+        <v>7358580</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590736</v>
+        <v>121590631</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>97073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733159</v>
+        <v>733042</v>
       </c>
       <c r="R3" t="n">
-        <v>7358335</v>
+        <v>7358712</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590742</v>
+        <v>121590726</v>
       </c>
       <c r="B4" t="n">
-        <v>77993</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733122</v>
+        <v>733444</v>
       </c>
       <c r="R4" t="n">
-        <v>7358420</v>
+        <v>7358349</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590746</v>
+        <v>121590735</v>
       </c>
       <c r="B5" t="n">
-        <v>79227</v>
+        <v>92032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>732917</v>
+        <v>733263</v>
       </c>
       <c r="R5" t="n">
-        <v>7358580</v>
+        <v>7358369</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590763</v>
+        <v>121590762</v>
       </c>
       <c r="B6" t="n">
-        <v>92012</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1116,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>732706</v>
+        <v>732698</v>
       </c>
       <c r="R6" t="n">
-        <v>7358642</v>
+        <v>7358638</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590632</v>
+        <v>121590747</v>
       </c>
       <c r="B7" t="n">
-        <v>82393</v>
+        <v>77548</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>732883</v>
+        <v>732908</v>
       </c>
       <c r="R7" t="n">
-        <v>7358415</v>
+        <v>7358595</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590758</v>
+        <v>121590759</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>90975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1368,7 +1368,7 @@
         <v>732625</v>
       </c>
       <c r="R8" t="n">
-        <v>7358560</v>
+        <v>7358605</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590727</v>
+        <v>121590736</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,30 +1444,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733444</v>
+        <v>733159</v>
       </c>
       <c r="R9" t="n">
-        <v>7358349</v>
+        <v>7358335</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,11 +1512,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590751</v>
+        <v>121590760</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1587,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>732715</v>
+        <v>732679</v>
       </c>
       <c r="R10" t="n">
-        <v>7358583</v>
+        <v>7358623</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590747</v>
+        <v>121590764</v>
       </c>
       <c r="B11" t="n">
-        <v>77541</v>
+        <v>91998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,26 +1660,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>732908</v>
+        <v>732711</v>
       </c>
       <c r="R11" t="n">
-        <v>7358595</v>
+        <v>7358653</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1729,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590744</v>
+        <v>121590730</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1804,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733121</v>
+        <v>733305</v>
       </c>
       <c r="R12" t="n">
-        <v>7358408</v>
+        <v>7358389</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,7 +1834,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590735</v>
+        <v>121590742</v>
       </c>
       <c r="B13" t="n">
-        <v>92024</v>
+        <v>78000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,26 +1877,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1915,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733263</v>
+        <v>733122</v>
       </c>
       <c r="R13" t="n">
-        <v>7358369</v>
+        <v>7358420</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,6 +1941,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590733</v>
+        <v>121590751</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>92004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,50 +1984,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733285</v>
+        <v>732715</v>
       </c>
       <c r="R14" t="n">
-        <v>7358339</v>
+        <v>7358583</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2065,11 +2052,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590757</v>
+        <v>121590733</v>
       </c>
       <c r="B15" t="n">
-        <v>78691</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,21 +2094,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2134,16 +2116,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>732625</v>
+        <v>733285</v>
       </c>
       <c r="R15" t="n">
-        <v>7358580</v>
+        <v>7358339</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2180,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2207,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590748</v>
+        <v>121590729</v>
       </c>
       <c r="B16" t="n">
-        <v>91988</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,30 +2209,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2251,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>732822</v>
+        <v>733332</v>
       </c>
       <c r="R16" t="n">
-        <v>7358527</v>
+        <v>7358386</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2313,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590636</v>
+        <v>121590758</v>
       </c>
       <c r="B17" t="n">
-        <v>97065</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,25 +2315,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733108</v>
+        <v>732625</v>
       </c>
       <c r="R17" t="n">
-        <v>7358536</v>
+        <v>7358560</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2387,12 +2377,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590764</v>
+        <v>121590728</v>
       </c>
       <c r="B18" t="n">
-        <v>91990</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,26 +2430,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2463,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>732711</v>
+        <v>733332</v>
       </c>
       <c r="R18" t="n">
-        <v>7358653</v>
+        <v>7358429</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2499,6 +2494,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590767</v>
+        <v>121590752</v>
       </c>
       <c r="B19" t="n">
-        <v>79718</v>
+        <v>57510</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2563,16 +2563,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>732723</v>
+        <v>732711</v>
       </c>
       <c r="R19" t="n">
-        <v>7358678</v>
+        <v>7358587</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2605,6 +2613,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2644,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590728</v>
+        <v>121590727</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>82400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2660,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2675,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733332</v>
+        <v>733444</v>
       </c>
       <c r="R20" t="n">
-        <v>7358429</v>
+        <v>7358349</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,7 +2728,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tallöverståndare</t>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590745</v>
+        <v>121590637</v>
       </c>
       <c r="B21" t="n">
-        <v>89769</v>
+        <v>57510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2758,21 +2771,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2780,16 +2793,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>732960</v>
+        <v>733345</v>
       </c>
       <c r="R21" t="n">
-        <v>7358509</v>
+        <v>7358499</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2816,12 +2837,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590743</v>
+        <v>121590731</v>
       </c>
       <c r="B22" t="n">
-        <v>77541</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2864,21 +2890,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2892,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733124</v>
+        <v>733309</v>
       </c>
       <c r="R22" t="n">
-        <v>7358421</v>
+        <v>7358348</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2932,7 +2958,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590761</v>
+        <v>121590749</v>
       </c>
       <c r="B23" t="n">
-        <v>92012</v>
+        <v>91998</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,26 +3001,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3003,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>732713</v>
+        <v>732814</v>
       </c>
       <c r="R23" t="n">
-        <v>7358624</v>
+        <v>7358528</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3065,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590726</v>
+        <v>121590766</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,7 +3126,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3109,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733444</v>
+        <v>732714</v>
       </c>
       <c r="R24" t="n">
-        <v>7358349</v>
+        <v>7358659</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3171,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590730</v>
+        <v>121590746</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
+        <v>79234</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3183,25 +3209,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3215,10 +3241,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733305</v>
+        <v>732917</v>
       </c>
       <c r="R25" t="n">
-        <v>7358389</v>
+        <v>7358580</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3255,7 +3281,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grov gammal sälg</t>
+          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,10 +3308,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590631</v>
+        <v>121590763</v>
       </c>
       <c r="B26" t="n">
-        <v>97065</v>
+        <v>92020</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,25 +3320,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3326,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733042</v>
+        <v>732706</v>
       </c>
       <c r="R26" t="n">
-        <v>7358712</v>
+        <v>7358642</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3356,12 +3382,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3414,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590750</v>
+        <v>121590761</v>
       </c>
       <c r="B27" t="n">
-        <v>91990</v>
+        <v>92020</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,26 +3430,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3432,10 +3458,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>732744</v>
+        <v>732713</v>
       </c>
       <c r="R27" t="n">
-        <v>7358602</v>
+        <v>7358624</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3494,10 +3520,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590749</v>
+        <v>121590765</v>
       </c>
       <c r="B28" t="n">
-        <v>91990</v>
+        <v>92004</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,30 +3532,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3538,10 +3564,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>732814</v>
+        <v>732711</v>
       </c>
       <c r="R28" t="n">
-        <v>7358528</v>
+        <v>7358653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3600,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590729</v>
+        <v>121590748</v>
       </c>
       <c r="B29" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,30 +3638,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3644,10 +3670,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733332</v>
+        <v>732822</v>
       </c>
       <c r="R29" t="n">
-        <v>7358386</v>
+        <v>7358527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3706,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590756</v>
+        <v>121590636</v>
       </c>
       <c r="B30" t="n">
-        <v>97059</v>
+        <v>97073</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3722,16 +3748,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3750,10 +3776,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>732650</v>
+        <v>733108</v>
       </c>
       <c r="R30" t="n">
-        <v>7358579</v>
+        <v>7358536</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3780,12 +3806,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3812,10 +3838,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590760</v>
+        <v>121590632</v>
       </c>
       <c r="B31" t="n">
-        <v>91996</v>
+        <v>82400</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3824,30 +3850,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3856,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>732679</v>
+        <v>732883</v>
       </c>
       <c r="R31" t="n">
-        <v>7358623</v>
+        <v>7358415</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3886,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3918,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590637</v>
+        <v>121590743</v>
       </c>
       <c r="B32" t="n">
-        <v>57509</v>
+        <v>77548</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3934,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3956,24 +3982,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733345</v>
+        <v>733124</v>
       </c>
       <c r="R32" t="n">
-        <v>7358499</v>
+        <v>7358421</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4000,17 +4018,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4037,10 +4055,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590731</v>
+        <v>121590750</v>
       </c>
       <c r="B33" t="n">
-        <v>82393</v>
+        <v>91998</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4053,26 +4071,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4081,10 +4099,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733309</v>
+        <v>732744</v>
       </c>
       <c r="R33" t="n">
-        <v>7358348</v>
+        <v>7358602</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4117,11 +4135,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590752</v>
+        <v>121590744</v>
       </c>
       <c r="B34" t="n">
-        <v>57509</v>
+        <v>79205</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4164,21 +4177,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4186,24 +4199,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732711</v>
+        <v>733121</v>
       </c>
       <c r="R34" t="n">
-        <v>7358587</v>
+        <v>7358408</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4267,10 +4272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590759</v>
+        <v>121590745</v>
       </c>
       <c r="B35" t="n">
-        <v>90967</v>
+        <v>89776</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,25 +4284,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4311,10 +4316,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732625</v>
+        <v>732960</v>
       </c>
       <c r="R35" t="n">
-        <v>7358605</v>
+        <v>7358509</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4347,11 +4352,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590765</v>
+        <v>121590756</v>
       </c>
       <c r="B36" t="n">
-        <v>91996</v>
+        <v>97067</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4394,26 +4394,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732711</v>
+        <v>732650</v>
       </c>
       <c r="R36" t="n">
-        <v>7358653</v>
+        <v>7358579</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590762</v>
+        <v>121590767</v>
       </c>
       <c r="B37" t="n">
-        <v>91996</v>
+        <v>79725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4500,26 +4500,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732698</v>
+        <v>732723</v>
       </c>
       <c r="R37" t="n">
-        <v>7358638</v>
+        <v>7358678</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590764</v>
+        <v>121590730</v>
       </c>
       <c r="B11" t="n">
-        <v>91998</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,30 +1656,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>732711</v>
+        <v>733305</v>
       </c>
       <c r="R11" t="n">
-        <v>7358653</v>
+        <v>7358389</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590730</v>
+        <v>121590764</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>91998</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,30 +1767,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1794,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733305</v>
+        <v>732711</v>
       </c>
       <c r="R12" t="n">
-        <v>7358389</v>
+        <v>7358653</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,11 +1835,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3520,10 +3520,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590765</v>
+        <v>121590632</v>
       </c>
       <c r="B28" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3532,30 +3532,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>732711</v>
+        <v>732883</v>
       </c>
       <c r="R28" t="n">
-        <v>7358653</v>
+        <v>7358415</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590748</v>
+        <v>121590743</v>
       </c>
       <c r="B29" t="n">
-        <v>91996</v>
+        <v>77548</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3642,26 +3642,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>732822</v>
+        <v>733124</v>
       </c>
       <c r="R29" t="n">
-        <v>7358527</v>
+        <v>7358421</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3706,6 +3706,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3737,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590636</v>
+        <v>121590765</v>
       </c>
       <c r="B30" t="n">
-        <v>97073</v>
+        <v>92004</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3748,26 +3753,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3776,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733108</v>
+        <v>732711</v>
       </c>
       <c r="R30" t="n">
-        <v>7358536</v>
+        <v>7358653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3806,12 +3811,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,10 +3843,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590632</v>
+        <v>121590748</v>
       </c>
       <c r="B31" t="n">
-        <v>82400</v>
+        <v>91996</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,26 +3859,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>732883</v>
+        <v>732822</v>
       </c>
       <c r="R31" t="n">
-        <v>7358415</v>
+        <v>7358527</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3912,12 +3917,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590743</v>
+        <v>121590636</v>
       </c>
       <c r="B32" t="n">
-        <v>77548</v>
+        <v>97073</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3961,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733124</v>
+        <v>733108</v>
       </c>
       <c r="R32" t="n">
-        <v>7358421</v>
+        <v>7358536</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4018,17 +4023,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590730</v>
+        <v>121590764</v>
       </c>
       <c r="B11" t="n">
-        <v>79733</v>
+        <v>91998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,30 +1656,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733305</v>
+        <v>732711</v>
       </c>
       <c r="R11" t="n">
-        <v>7358389</v>
+        <v>7358653</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590764</v>
+        <v>121590730</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,30 +1762,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1799,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>732711</v>
+        <v>733305</v>
       </c>
       <c r="R12" t="n">
-        <v>7358653</v>
+        <v>7358389</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,6 +1830,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590759</v>
+        <v>121590726</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732625</v>
+        <v>733444</v>
       </c>
       <c r="R2" t="n">
-        <v>7358605</v>
+        <v>7358349</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590745</v>
+        <v>121590733</v>
       </c>
       <c r="B3" t="n">
-        <v>89776</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,16 +819,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>732960</v>
+        <v>733285</v>
       </c>
       <c r="R3" t="n">
-        <v>7358509</v>
+        <v>7358339</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590743</v>
+        <v>121590631</v>
       </c>
       <c r="B4" t="n">
-        <v>77548</v>
+        <v>97073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733124</v>
+        <v>733042</v>
       </c>
       <c r="R4" t="n">
-        <v>7358421</v>
+        <v>7358712</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,17 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590750</v>
+        <v>121590767</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>79725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,30 +1018,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>732744</v>
+        <v>732723</v>
       </c>
       <c r="R5" t="n">
-        <v>7358602</v>
+        <v>7358678</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590733</v>
+        <v>121590761</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,24 +1150,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733285</v>
+        <v>732713</v>
       </c>
       <c r="R6" t="n">
-        <v>7358339</v>
+        <v>7358624</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,11 +1192,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590765</v>
+        <v>121590744</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>79205</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,30 +1230,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1272,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>732711</v>
+        <v>733121</v>
       </c>
       <c r="R7" t="n">
-        <v>7358653</v>
+        <v>7358408</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590758</v>
+        <v>121590735</v>
       </c>
       <c r="B8" t="n">
-        <v>82400</v>
+        <v>92032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,26 +1345,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1378,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>732625</v>
+        <v>733263</v>
       </c>
       <c r="R8" t="n">
-        <v>7358560</v>
+        <v>7358369</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590766</v>
+        <v>121590727</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,30 +1447,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>732714</v>
+        <v>733444</v>
       </c>
       <c r="R9" t="n">
-        <v>7358659</v>
+        <v>7358349</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590748</v>
+        <v>121590742</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>78000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,26 +1562,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>732822</v>
+        <v>733122</v>
       </c>
       <c r="R10" t="n">
-        <v>7358527</v>
+        <v>7358420</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,6 +1626,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590761</v>
+        <v>121590759</v>
       </c>
       <c r="B11" t="n">
-        <v>92020</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,25 +1669,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>732713</v>
+        <v>732625</v>
       </c>
       <c r="R11" t="n">
-        <v>7358624</v>
+        <v>7358605</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1737,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590764</v>
+        <v>121590729</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>97067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,30 +1780,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>732711</v>
+        <v>733332</v>
       </c>
       <c r="R12" t="n">
-        <v>7358653</v>
+        <v>7358386</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1869,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590749</v>
+        <v>121590745</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>89776</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,26 +1890,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>732814</v>
+        <v>732960</v>
       </c>
       <c r="R13" t="n">
-        <v>7358528</v>
+        <v>7358509</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590728</v>
+        <v>121590730</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,25 +1992,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733332</v>
+        <v>733305</v>
       </c>
       <c r="R14" t="n">
-        <v>7358429</v>
+        <v>7358389</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2064,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gammal tallöverståndare</t>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590727</v>
+        <v>121590750</v>
       </c>
       <c r="B15" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,26 +2107,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2130,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733444</v>
+        <v>732744</v>
       </c>
       <c r="R15" t="n">
-        <v>7358349</v>
+        <v>7358602</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2166,11 +2171,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590763</v>
+        <v>121590728</v>
       </c>
       <c r="B16" t="n">
-        <v>92020</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>732706</v>
+        <v>733332</v>
       </c>
       <c r="R16" t="n">
-        <v>7358642</v>
+        <v>7358429</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,6 +2277,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590756</v>
+        <v>121590632</v>
       </c>
       <c r="B17" t="n">
-        <v>97067</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,25 +2320,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>732650</v>
+        <v>732883</v>
       </c>
       <c r="R17" t="n">
-        <v>7358579</v>
+        <v>7358415</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2377,12 +2382,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590729</v>
+        <v>121590751</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>92004</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,26 +2430,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733332</v>
+        <v>732715</v>
       </c>
       <c r="R18" t="n">
-        <v>7358386</v>
+        <v>7358583</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2515,10 +2520,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590744</v>
+        <v>121590749</v>
       </c>
       <c r="B19" t="n">
-        <v>79205</v>
+        <v>91998</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,26 +2536,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733121</v>
+        <v>732814</v>
       </c>
       <c r="R19" t="n">
-        <v>7358408</v>
+        <v>7358528</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2595,11 +2600,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590735</v>
+        <v>121590748</v>
       </c>
       <c r="B20" t="n">
-        <v>92032</v>
+        <v>91996</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,26 +2642,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733263</v>
+        <v>732822</v>
       </c>
       <c r="R20" t="n">
-        <v>7358369</v>
+        <v>7358527</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590747</v>
+        <v>121590746</v>
       </c>
       <c r="B21" t="n">
-        <v>77548</v>
+        <v>79234</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>732908</v>
+        <v>732917</v>
       </c>
       <c r="R21" t="n">
-        <v>7358595</v>
+        <v>7358580</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammalt talltorrträd</t>
+          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590757</v>
+        <v>121590747</v>
       </c>
       <c r="B22" t="n">
-        <v>78698</v>
+        <v>77548</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732625</v>
+        <v>732908</v>
       </c>
       <c r="R22" t="n">
-        <v>7358580</v>
+        <v>7358595</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590631</v>
+        <v>121590758</v>
       </c>
       <c r="B23" t="n">
-        <v>97073</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,25 +2966,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733042</v>
+        <v>732625</v>
       </c>
       <c r="R23" t="n">
-        <v>7358712</v>
+        <v>7358560</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3028,12 +3028,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590760</v>
+        <v>121590763</v>
       </c>
       <c r="B24" t="n">
-        <v>92004</v>
+        <v>92020</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3072,30 +3077,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>732679</v>
+        <v>732706</v>
       </c>
       <c r="R24" t="n">
-        <v>7358623</v>
+        <v>7358642</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3166,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590767</v>
+        <v>121590743</v>
       </c>
       <c r="B25" t="n">
-        <v>79725</v>
+        <v>77548</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,25 +3183,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3210,10 +3215,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>732723</v>
+        <v>733124</v>
       </c>
       <c r="R25" t="n">
-        <v>7358678</v>
+        <v>7358421</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3246,6 +3251,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590637</v>
+        <v>121590731</v>
       </c>
       <c r="B26" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3288,21 +3298,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3310,24 +3320,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733345</v>
+        <v>733309</v>
       </c>
       <c r="R26" t="n">
-        <v>7358499</v>
+        <v>7358348</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3354,17 +3356,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590736</v>
+        <v>121590752</v>
       </c>
       <c r="B27" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,42 +3405,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733159</v>
+        <v>732711</v>
       </c>
       <c r="R27" t="n">
-        <v>7358335</v>
+        <v>7358587</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3471,6 +3481,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3497,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590726</v>
+        <v>121590757</v>
       </c>
       <c r="B28" t="n">
-        <v>92004</v>
+        <v>78698</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,30 +3524,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3541,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733444</v>
+        <v>732625</v>
       </c>
       <c r="R28" t="n">
-        <v>7358349</v>
+        <v>7358580</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3577,6 +3592,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590746</v>
+        <v>121590636</v>
       </c>
       <c r="B29" t="n">
-        <v>79234</v>
+        <v>97073</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,25 +3635,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3647,10 +3667,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>732917</v>
+        <v>733108</v>
       </c>
       <c r="R29" t="n">
-        <v>7358580</v>
+        <v>7358536</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3677,17 +3697,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gammal kolad tallstubbe</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,10 +3729,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590730</v>
+        <v>121590756</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>97067</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,21 +3745,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3758,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733305</v>
+        <v>732650</v>
       </c>
       <c r="R30" t="n">
-        <v>7358389</v>
+        <v>7358579</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3794,11 +3809,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3835,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590742</v>
+        <v>121590736</v>
       </c>
       <c r="B31" t="n">
-        <v>78000</v>
+        <v>92004</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,30 +3847,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3869,10 +3879,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733122</v>
+        <v>733159</v>
       </c>
       <c r="R31" t="n">
-        <v>7358420</v>
+        <v>7358335</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3905,11 +3915,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,10 +3941,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590636</v>
+        <v>121590762</v>
       </c>
       <c r="B32" t="n">
-        <v>97073</v>
+        <v>92004</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3952,26 +3957,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3980,10 +3985,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733108</v>
+        <v>732698</v>
       </c>
       <c r="R32" t="n">
-        <v>7358536</v>
+        <v>7358638</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4010,12 +4015,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4042,10 +4047,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590731</v>
+        <v>121590765</v>
       </c>
       <c r="B33" t="n">
-        <v>82400</v>
+        <v>92004</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4054,30 +4059,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4086,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733309</v>
+        <v>732711</v>
       </c>
       <c r="R33" t="n">
-        <v>7358348</v>
+        <v>7358653</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4122,11 +4127,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590751</v>
+        <v>121590637</v>
       </c>
       <c r="B34" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,42 +4165,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732715</v>
+        <v>733345</v>
       </c>
       <c r="R34" t="n">
-        <v>7358583</v>
+        <v>7358499</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,12 +4235,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,10 +4272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590752</v>
+        <v>121590766</v>
       </c>
       <c r="B35" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4271,50 +4284,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732711</v>
+        <v>732714</v>
       </c>
       <c r="R35" t="n">
-        <v>7358587</v>
+        <v>7358659</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4347,11 +4352,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590632</v>
+        <v>121590764</v>
       </c>
       <c r="B36" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4394,26 +4394,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732883</v>
+        <v>732711</v>
       </c>
       <c r="R36" t="n">
-        <v>7358415</v>
+        <v>7358653</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,7 +4484,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590762</v>
+        <v>121590760</v>
       </c>
       <c r="B37" t="n">
         <v>92004</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732698</v>
+        <v>732679</v>
       </c>
       <c r="R37" t="n">
-        <v>7358638</v>
+        <v>7358623</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590761</v>
+        <v>121590735</v>
       </c>
       <c r="B6" t="n">
-        <v>92020</v>
+        <v>92032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,26 +1128,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>732713</v>
+        <v>733263</v>
       </c>
       <c r="R6" t="n">
-        <v>7358624</v>
+        <v>7358369</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590744</v>
+        <v>121590761</v>
       </c>
       <c r="B7" t="n">
-        <v>79205</v>
+        <v>92020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733121</v>
+        <v>732713</v>
       </c>
       <c r="R7" t="n">
-        <v>7358408</v>
+        <v>7358624</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590735</v>
+        <v>121590744</v>
       </c>
       <c r="B8" t="n">
-        <v>92032</v>
+        <v>79205</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,26 +1340,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1373,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733263</v>
+        <v>733121</v>
       </c>
       <c r="R8" t="n">
-        <v>7358369</v>
+        <v>7358408</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590750</v>
+        <v>121590751</v>
       </c>
       <c r="B15" t="n">
-        <v>91998</v>
+        <v>92004</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,25 +2103,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>732744</v>
+        <v>732715</v>
       </c>
       <c r="R15" t="n">
-        <v>7358602</v>
+        <v>7358583</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590728</v>
+        <v>121590750</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>91998</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,26 +2213,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733332</v>
+        <v>732744</v>
       </c>
       <c r="R16" t="n">
-        <v>7358429</v>
+        <v>7358602</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,11 +2277,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590632</v>
+        <v>121590728</v>
       </c>
       <c r="B17" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,21 +2319,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>732883</v>
+        <v>733332</v>
       </c>
       <c r="R17" t="n">
-        <v>7358415</v>
+        <v>7358429</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,12 +2377,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590751</v>
+        <v>121590632</v>
       </c>
       <c r="B18" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,30 +2426,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>732715</v>
+        <v>732883</v>
       </c>
       <c r="R18" t="n">
-        <v>7358583</v>
+        <v>7358415</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590747</v>
+        <v>121590758</v>
       </c>
       <c r="B22" t="n">
-        <v>77548</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732908</v>
+        <v>732625</v>
       </c>
       <c r="R22" t="n">
-        <v>7358595</v>
+        <v>7358560</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammalt talltorrträd</t>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590758</v>
+        <v>121590747</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
+        <v>77548</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,21 +2970,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>732625</v>
+        <v>732908</v>
       </c>
       <c r="R23" t="n">
-        <v>7358560</v>
+        <v>7358595</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran</t>
+          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590731</v>
+        <v>121590752</v>
       </c>
       <c r="B26" t="n">
-        <v>82400</v>
+        <v>57510</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,21 +3298,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3320,16 +3320,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733309</v>
+        <v>732711</v>
       </c>
       <c r="R26" t="n">
-        <v>7358348</v>
+        <v>7358587</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3366,7 +3374,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3401,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590752</v>
+        <v>121590731</v>
       </c>
       <c r="B27" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3409,21 +3417,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3431,24 +3439,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>732711</v>
+        <v>733309</v>
       </c>
       <c r="R27" t="n">
-        <v>7358587</v>
+        <v>7358348</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590757</v>
+        <v>121590636</v>
       </c>
       <c r="B28" t="n">
-        <v>78698</v>
+        <v>97073</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,25 +3524,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>732625</v>
+        <v>733108</v>
       </c>
       <c r="R28" t="n">
-        <v>7358580</v>
+        <v>7358536</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,17 +3586,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590636</v>
+        <v>121590757</v>
       </c>
       <c r="B29" t="n">
-        <v>97073</v>
+        <v>78698</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,25 +3630,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3667,10 +3662,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733108</v>
+        <v>732625</v>
       </c>
       <c r="R29" t="n">
-        <v>7358536</v>
+        <v>7358580</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,12 +3692,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23337-2020 artfynd.xlsx
+++ b/artfynd/A 23337-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590726</v>
+        <v>121590761</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733444</v>
+        <v>732713</v>
       </c>
       <c r="R2" t="n">
-        <v>7358349</v>
+        <v>7358624</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590733</v>
+        <v>121590767</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>79725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,24 +819,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733285</v>
+        <v>732723</v>
       </c>
       <c r="R3" t="n">
-        <v>7358339</v>
+        <v>7358678</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590631</v>
+        <v>121590747</v>
       </c>
       <c r="B4" t="n">
-        <v>97073</v>
+        <v>77548</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733042</v>
+        <v>732908</v>
       </c>
       <c r="R4" t="n">
-        <v>7358712</v>
+        <v>7358595</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,12 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590767</v>
+        <v>121590746</v>
       </c>
       <c r="B5" t="n">
-        <v>79725</v>
+        <v>79234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>732723</v>
+        <v>732917</v>
       </c>
       <c r="R5" t="n">
-        <v>7358678</v>
+        <v>7358580</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590735</v>
+        <v>121590765</v>
       </c>
       <c r="B6" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,30 +1121,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1156,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733263</v>
+        <v>732711</v>
       </c>
       <c r="R6" t="n">
-        <v>7358369</v>
+        <v>7358653</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590761</v>
+        <v>121590733</v>
       </c>
       <c r="B7" t="n">
-        <v>92020</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1256,16 +1253,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>732713</v>
+        <v>733285</v>
       </c>
       <c r="R7" t="n">
-        <v>7358624</v>
+        <v>7358339</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,6 +1303,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flygande, läte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590744</v>
+        <v>121590748</v>
       </c>
       <c r="B8" t="n">
-        <v>79205</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,26 +1350,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1368,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733121</v>
+        <v>732822</v>
       </c>
       <c r="R8" t="n">
-        <v>7358408</v>
+        <v>7358527</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,11 +1414,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590727</v>
+        <v>121590766</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,30 +1452,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1479,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733444</v>
+        <v>732714</v>
       </c>
       <c r="R9" t="n">
-        <v>7358349</v>
+        <v>7358659</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1515,11 +1520,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590742</v>
+        <v>121590751</v>
       </c>
       <c r="B10" t="n">
-        <v>78000</v>
+        <v>92004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,30 +1558,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733122</v>
+        <v>732715</v>
       </c>
       <c r="R10" t="n">
-        <v>7358420</v>
+        <v>7358583</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,11 +1626,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590759</v>
+        <v>121590749</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>91998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,30 +1664,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>732625</v>
+        <v>732814</v>
       </c>
       <c r="R11" t="n">
-        <v>7358605</v>
+        <v>7358528</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1737,11 +1732,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590729</v>
+        <v>121590752</v>
       </c>
       <c r="B12" t="n">
-        <v>97067</v>
+        <v>57510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,25 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1806,16 +1796,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733332</v>
+        <v>732711</v>
       </c>
       <c r="R12" t="n">
-        <v>7358386</v>
+        <v>7358587</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1848,6 +1846,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590745</v>
+        <v>121590743</v>
       </c>
       <c r="B13" t="n">
-        <v>89776</v>
+        <v>77548</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,21 +1893,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1918,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>732960</v>
+        <v>733124</v>
       </c>
       <c r="R13" t="n">
-        <v>7358509</v>
+        <v>7358421</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1954,6 +1957,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590730</v>
+        <v>121590758</v>
       </c>
       <c r="B14" t="n">
-        <v>79733</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,25 +2000,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2024,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733305</v>
+        <v>732625</v>
       </c>
       <c r="R14" t="n">
-        <v>7358389</v>
+        <v>7358560</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2064,7 +2072,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På grov gammal sälg</t>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2099,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590751</v>
+        <v>121590759</v>
       </c>
       <c r="B15" t="n">
-        <v>92004</v>
+        <v>90975</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,30 +2111,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2135,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>732715</v>
+        <v>732625</v>
       </c>
       <c r="R15" t="n">
-        <v>7358583</v>
+        <v>7358605</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2171,6 +2179,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal halvt nedbruten barrved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590750</v>
+        <v>121590735</v>
       </c>
       <c r="B16" t="n">
-        <v>91998</v>
+        <v>92032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,26 +2226,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2241,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>732744</v>
+        <v>733263</v>
       </c>
       <c r="R16" t="n">
-        <v>7358602</v>
+        <v>7358369</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590728</v>
+        <v>121590762</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>92004</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,30 +2328,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2347,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733332</v>
+        <v>732698</v>
       </c>
       <c r="R17" t="n">
-        <v>7358429</v>
+        <v>7358638</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2383,11 +2396,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590632</v>
+        <v>121590756</v>
       </c>
       <c r="B18" t="n">
-        <v>82400</v>
+        <v>97067</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,25 +2434,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2458,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>732883</v>
+        <v>732650</v>
       </c>
       <c r="R18" t="n">
-        <v>7358415</v>
+        <v>7358579</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2488,12 +2496,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590749</v>
+        <v>121590757</v>
       </c>
       <c r="B19" t="n">
-        <v>91998</v>
+        <v>78698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2536,26 +2544,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2564,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>732814</v>
+        <v>732625</v>
       </c>
       <c r="R19" t="n">
-        <v>7358528</v>
+        <v>7358580</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2600,6 +2608,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,10 +2639,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590748</v>
+        <v>121590750</v>
       </c>
       <c r="B20" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2642,26 +2655,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2670,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>732822</v>
+        <v>732744</v>
       </c>
       <c r="R20" t="n">
-        <v>7358527</v>
+        <v>7358602</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2732,10 +2745,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590746</v>
+        <v>121590727</v>
       </c>
       <c r="B21" t="n">
-        <v>79234</v>
+        <v>82400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,21 +2761,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2776,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>732917</v>
+        <v>733444</v>
       </c>
       <c r="R21" t="n">
-        <v>7358580</v>
+        <v>7358349</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2816,7 +2829,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gammal kolad tallstubbe</t>
+          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590758</v>
+        <v>121590636</v>
       </c>
       <c r="B22" t="n">
-        <v>82400</v>
+        <v>97073</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,25 +2868,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2887,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732625</v>
+        <v>733108</v>
       </c>
       <c r="R22" t="n">
-        <v>7358560</v>
+        <v>7358536</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2917,17 +2930,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2954,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590747</v>
+        <v>121590731</v>
       </c>
       <c r="B23" t="n">
-        <v>77548</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2970,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2998,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>732908</v>
+        <v>733309</v>
       </c>
       <c r="R23" t="n">
-        <v>7358595</v>
+        <v>7358348</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3038,7 +3046,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammalt talltorrträd</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590763</v>
+        <v>121590745</v>
       </c>
       <c r="B24" t="n">
-        <v>92020</v>
+        <v>89776</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,21 +3089,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3109,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>732706</v>
+        <v>732960</v>
       </c>
       <c r="R24" t="n">
-        <v>7358642</v>
+        <v>7358509</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3171,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590743</v>
+        <v>121590763</v>
       </c>
       <c r="B25" t="n">
-        <v>77548</v>
+        <v>92020</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,21 +3195,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3215,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733124</v>
+        <v>732706</v>
       </c>
       <c r="R25" t="n">
-        <v>7358421</v>
+        <v>7358642</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3251,11 +3259,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590752</v>
+        <v>121590730</v>
       </c>
       <c r="B26" t="n">
-        <v>57510</v>
+        <v>79733</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,25 +3297,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3320,24 +3323,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>732711</v>
+        <v>733305</v>
       </c>
       <c r="R26" t="n">
-        <v>7358587</v>
+        <v>7358389</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3374,7 +3369,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Varnande läte</t>
+          <t>På grov gammal sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3401,10 +3396,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590731</v>
+        <v>121590764</v>
       </c>
       <c r="B27" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3417,26 +3412,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3445,10 +3440,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733309</v>
+        <v>732711</v>
       </c>
       <c r="R27" t="n">
-        <v>7358348</v>
+        <v>7358653</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3481,11 +3476,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,10 +3502,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590636</v>
+        <v>121590726</v>
       </c>
       <c r="B28" t="n">
-        <v>97073</v>
+        <v>92004</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3528,26 +3518,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3556,10 +3546,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733108</v>
+        <v>733444</v>
       </c>
       <c r="R28" t="n">
-        <v>7358536</v>
+        <v>7358349</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,12 +3576,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590757</v>
+        <v>121590760</v>
       </c>
       <c r="B29" t="n">
-        <v>78698</v>
+        <v>92004</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3630,30 +3620,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3662,10 +3652,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>732625</v>
+        <v>732679</v>
       </c>
       <c r="R29" t="n">
-        <v>7358580</v>
+        <v>7358623</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3698,11 +3688,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590756</v>
+        <v>121590728</v>
       </c>
       <c r="B30" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3741,25 +3726,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3773,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>732650</v>
+        <v>733332</v>
       </c>
       <c r="R30" t="n">
-        <v>7358579</v>
+        <v>7358429</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,6 +3794,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tallöverståndare</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,10 +3931,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590762</v>
+        <v>121590631</v>
       </c>
       <c r="B32" t="n">
-        <v>92004</v>
+        <v>97073</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3957,26 +3947,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3985,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>732698</v>
+        <v>733042</v>
       </c>
       <c r="R32" t="n">
-        <v>7358638</v>
+        <v>7358712</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4015,12 +4005,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4047,10 +4037,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590765</v>
+        <v>121590744</v>
       </c>
       <c r="B33" t="n">
-        <v>92004</v>
+        <v>79205</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4059,30 +4049,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4091,10 +4081,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>732711</v>
+        <v>733121</v>
       </c>
       <c r="R33" t="n">
-        <v>7358653</v>
+        <v>7358408</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4127,6 +4117,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590637</v>
+        <v>121590632</v>
       </c>
       <c r="B34" t="n">
-        <v>57510</v>
+        <v>82400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4169,21 +4164,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4191,24 +4186,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733345</v>
+        <v>732883</v>
       </c>
       <c r="R34" t="n">
-        <v>7358499</v>
+        <v>7358415</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4241,11 +4228,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4272,10 +4254,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590766</v>
+        <v>121590742</v>
       </c>
       <c r="B35" t="n">
-        <v>92004</v>
+        <v>78000</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4284,30 +4266,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4316,10 +4298,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732714</v>
+        <v>733122</v>
       </c>
       <c r="R35" t="n">
-        <v>7358659</v>
+        <v>7358420</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4352,6 +4334,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590764</v>
+        <v>121590637</v>
       </c>
       <c r="B36" t="n">
-        <v>91998</v>
+        <v>57510</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4394,38 +4381,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732711</v>
+        <v>733345</v>
       </c>
       <c r="R36" t="n">
-        <v>7358653</v>
+        <v>7358499</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4452,12 +4447,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590760</v>
+        <v>121590729</v>
       </c>
       <c r="B37" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4500,26 +4500,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732679</v>
+        <v>733332</v>
       </c>
       <c r="R37" t="n">
-        <v>7358623</v>
+        <v>7358386</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
